--- a/data-source/COMPRAPARAGUAI.xlsx
+++ b/data-source/COMPRAPARAGUAI.xlsx
@@ -160,6 +160,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/data-source/COMPRAPARAGUAI.xlsx
+++ b/data-source/COMPRAPARAGUAI.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/SMART-STOCK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{0945D746-136B-4EA6-8FA1-116932EBA3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB93799D-EE89-408E-A73D-30D29D386CA1}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{0945D746-136B-4EA6-8FA1-116932EBA3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84725C80-E1AC-4EC5-B161-CB3F226885D6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EC661E31-7BDC-4492-BDCF-C8B212342257}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="8">
   <si>
     <t>Produto</t>
   </si>
@@ -97,7 +97,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -107,6 +107,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC0C0C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,14 +143,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -483,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65630E9C-5564-429A-8139-A7EDF74685C9}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
@@ -511,16 +518,16 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="A2" s="2">
         <v>9010</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="4">
@@ -528,16 +535,16 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+      <c r="A3" s="5">
         <v>15721</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E3" s="4">
@@ -545,88 +552,71 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="A4" s="5">
         <v>15721</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>13</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E4">
-        <v>30610</v>
+      <c r="E4" s="2">
+        <v>21000</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <v>15721</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5">
+      <c r="A5" s="5">
+        <v>9010</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="2">
         <v>13</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E5">
-        <v>21000</v>
+      <c r="E5" s="2">
+        <v>7000</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <v>9010</v>
+      <c r="A6" s="2">
+        <v>15721</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2">
         <v>13</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E6">
-        <v>7000</v>
+      <c r="E6" s="2">
+        <v>21000</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>15721</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7">
+      <c r="A7" s="2">
+        <v>9010</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="2">
         <v>13</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2">
         <v>10000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>9010</v>
-      </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8">
-        <v>21000</v>
       </c>
     </row>
   </sheetData>

--- a/data-source/COMPRAPARAGUAI.xlsx
+++ b/data-source/COMPRAPARAGUAI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/SMART-STOCK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{0945D746-136B-4EA6-8FA1-116932EBA3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84725C80-E1AC-4EC5-B161-CB3F226885D6}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{0945D746-136B-4EA6-8FA1-116932EBA3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C0B0D3C-FB15-40D0-B15D-F83306103F80}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EC661E31-7BDC-4492-BDCF-C8B212342257}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="8">
   <si>
     <t>Produto</t>
   </si>
@@ -167,10 +167,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -490,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65630E9C-5564-429A-8139-A7EDF74685C9}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
@@ -619,6 +615,40 @@
         <v>10000</v>
       </c>
     </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="2">
+        <v>15721</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2">
+        <v>13</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="2">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>9010</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2">
+        <v>13</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="2">
+        <v>10000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/data-source/COMPRAPARAGUAI.xlsx
+++ b/data-source/COMPRAPARAGUAI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b319cc1648f3add/Área de Trabalho/SMART-STOCK/data-source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{0945D746-136B-4EA6-8FA1-116932EBA3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C0B0D3C-FB15-40D0-B15D-F83306103F80}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="8_{0945D746-136B-4EA6-8FA1-116932EBA3E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4F0E881-F672-42D6-AFAB-2F1FF7E0754F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{EC661E31-7BDC-4492-BDCF-C8B212342257}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="8">
   <si>
     <t>Produto</t>
   </si>
@@ -486,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65630E9C-5564-429A-8139-A7EDF74685C9}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
@@ -646,7 +646,24 @@
         <v>6</v>
       </c>
       <c r="E9" s="2">
-        <v>10000</v>
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="2">
+        <v>15721</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2">
+        <v>13</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="2">
+        <v>31000</v>
       </c>
     </row>
   </sheetData>
